--- a/data/timeline.xlsx
+++ b/data/timeline.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepjadhav/Documents/GitHub/Sankalp Website/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepjadhav/Documents/GitHub/Sankalp Website/Sankalp_SJ/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5C4E29-6317-6F4C-89AE-EBD3AAF9C417}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A3EEB6-99CD-5142-90E4-B1726791BFA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -166,10 +166,10 @@
     <t>assets/images/events/2026/diwali.jpg</t>
   </si>
   <si>
-    <t>Makar Sankrant 2026</t>
-  </si>
-  <si>
     <t>Diwali 06</t>
+  </si>
+  <si>
+    <t>Makar Sankrant 2026 SJ</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -734,7 +734,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>46</v>
